--- a/AAII_Financials/Quarterly/MAAS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAAS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>MAAS</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -714,23 +714,23 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>49000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>51000</v>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>141100</v>
+        <v>79100</v>
       </c>
       <c r="G8" s="3">
-        <v>142000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2400</v>
+        <v>79600</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J8" s="3">
         <v>3200</v>
@@ -743,23 +743,23 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>28700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>29900</v>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F9" s="3">
-        <v>86600</v>
+        <v>48700</v>
       </c>
       <c r="G9" s="3">
-        <v>87100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>600</v>
+        <v>49000</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J9" s="3">
         <v>400</v>
@@ -772,23 +772,23 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>20300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>21200</v>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>54500</v>
+        <v>30400</v>
       </c>
       <c r="G10" s="3">
-        <v>54800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1900</v>
+        <v>30600</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J10" s="3">
         <v>2800</v>
@@ -872,11 +872,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-36700</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-38200</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
         <v>34500</v>
@@ -902,10 +902,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>2000</v>
@@ -914,10 +914,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -940,23 +940,23 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>58700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>61000</v>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F17" s="3">
-        <v>117400</v>
+        <v>79500</v>
       </c>
       <c r="G17" s="3">
-        <v>118200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4300</v>
+        <v>80000</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J17" s="3">
         <v>4600</v>
@@ -969,23 +969,23 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-10000</v>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F18" s="3">
-        <v>23600</v>
+        <v>-400</v>
       </c>
       <c r="G18" s="3">
-        <v>23800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1900</v>
+        <v>-400</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J18" s="3">
         <v>-1400</v>
@@ -1011,23 +1011,23 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2400</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>24200</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>24300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
+        <v>200</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
@@ -1041,10 +1041,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-9900</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>-10300</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>1500</v>
@@ -1053,10 +1053,10 @@
         <v>-400</v>
       </c>
       <c r="H21" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-1200</v>
@@ -1098,11 +1098,11 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>26900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>28000</v>
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F23" s="3">
         <v>-32600</v>
@@ -1110,11 +1110,11 @@
       <c r="G23" s="3">
         <v>-32800</v>
       </c>
-      <c r="H23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1700</v>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
@@ -1127,11 +1127,11 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>5700</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>300</v>
@@ -1139,11 +1139,11 @@
       <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>500</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J24" s="3">
         <v>700</v>
@@ -1185,11 +1185,11 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>21500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>22300</v>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F26" s="3">
         <v>-32900</v>
@@ -1197,11 +1197,11 @@
       <c r="G26" s="3">
         <v>-33200</v>
       </c>
-      <c r="H26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2300</v>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J26" s="3">
         <v>-800</v>
@@ -1214,11 +1214,11 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>15900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>16500</v>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F27" s="3">
         <v>-17700</v>
@@ -1226,11 +1226,11 @@
       <c r="G27" s="3">
         <v>-17800</v>
       </c>
-      <c r="H27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2300</v>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J27" s="3">
         <v>-800</v>
@@ -1359,23 +1359,23 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2400</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>-24200</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-24300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
+        <v>-200</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
@@ -1388,11 +1388,11 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>15900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>16500</v>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F33" s="3">
         <v>-17600</v>
@@ -1400,11 +1400,11 @@
       <c r="G33" s="3">
         <v>-17800</v>
       </c>
-      <c r="H33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2300</v>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J33" s="3">
         <v>-800</v>
@@ -1446,11 +1446,11 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>15900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>16500</v>
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F35" s="3">
         <v>-17600</v>
@@ -1458,11 +1458,11 @@
       <c r="G35" s="3">
         <v>-17800</v>
       </c>
-      <c r="H35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2300</v>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J35" s="3">
         <v>-800</v>
@@ -1535,11 +1535,11 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>37000</v>
-      </c>
-      <c r="E41" s="3">
-        <v>38500</v>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F41" s="3">
         <v>40700</v>
@@ -1547,11 +1547,11 @@
       <c r="G41" s="3">
         <v>41000</v>
       </c>
-      <c r="H41" s="3">
-        <v>83600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>81300</v>
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J41" s="3">
         <v>22700</v>
@@ -1565,10 +1565,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>84800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>88200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>82200</v>
@@ -1577,10 +1577,10 @@
         <v>82800</v>
       </c>
       <c r="H42" s="3">
-        <v>136600</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>132700</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1593,11 +1593,11 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>175600</v>
-      </c>
-      <c r="E43" s="3">
-        <v>182700</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F43" s="3">
         <v>192100</v>
@@ -1605,11 +1605,11 @@
       <c r="G43" s="3">
         <v>193400</v>
       </c>
-      <c r="H43" s="3">
-        <v>120000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>116600</v>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3">
         <v>8100</v>
@@ -1651,11 +1651,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5300</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>2000</v>
@@ -1663,11 +1663,11 @@
       <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
-        <v>25300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>24600</v>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
@@ -1680,11 +1680,11 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>307400</v>
-      </c>
-      <c r="E46" s="3">
-        <v>319800</v>
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F46" s="3">
         <v>328200</v>
@@ -1692,11 +1692,11 @@
       <c r="G46" s="3">
         <v>330400</v>
       </c>
-      <c r="H46" s="3">
-        <v>365500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>355200</v>
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J46" s="3">
         <v>31900</v>
@@ -1709,11 +1709,11 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>138000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>143600</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>19700</v>
@@ -1738,11 +1738,11 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>22000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>22900</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F48" s="3">
         <v>28800</v>
@@ -1750,11 +1750,11 @@
       <c r="G48" s="3">
         <v>28900</v>
       </c>
-      <c r="H48" s="3">
-        <v>33900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>33000</v>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J48" s="3">
         <v>2100</v>
@@ -1767,11 +1767,11 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>29900</v>
-      </c>
-      <c r="E49" s="3">
-        <v>31100</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F49" s="3">
         <v>90900</v>
@@ -1779,11 +1779,11 @@
       <c r="G49" s="3">
         <v>91500</v>
       </c>
-      <c r="H49" s="3">
-        <v>160700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>156200</v>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -1854,11 +1854,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>31600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>32900</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3">
         <v>12000</v>
@@ -1866,11 +1866,11 @@
       <c r="G52" s="3">
         <v>12100</v>
       </c>
-      <c r="H52" s="3">
-        <v>134800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>131000</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -1912,11 +1912,11 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>625200</v>
-      </c>
-      <c r="E54" s="3">
-        <v>650600</v>
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F54" s="3">
         <v>588700</v>
@@ -1924,11 +1924,11 @@
       <c r="G54" s="3">
         <v>592500</v>
       </c>
-      <c r="H54" s="3">
-        <v>701600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>681900</v>
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J54" s="3">
         <v>36500</v>
@@ -1967,11 +1967,11 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>16000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>16600</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F57" s="3">
         <v>26700</v>
@@ -1979,11 +1979,11 @@
       <c r="G57" s="3">
         <v>26900</v>
       </c>
-      <c r="H57" s="3">
-        <v>57900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>56200</v>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J57" s="3">
         <v>900</v>
@@ -1996,11 +1996,11 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>24000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>25000</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>21000</v>
@@ -2008,11 +2008,11 @@
       <c r="G58" s="3">
         <v>21100</v>
       </c>
-      <c r="H58" s="3">
-        <v>31900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>31000</v>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
@@ -2025,11 +2025,11 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>47400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>49300</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F59" s="3">
         <v>23200</v>
@@ -2037,11 +2037,11 @@
       <c r="G59" s="3">
         <v>23300</v>
       </c>
-      <c r="H59" s="3">
-        <v>42500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>41300</v>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
@@ -2054,11 +2054,11 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>114100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>118700</v>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F60" s="3">
         <v>117100</v>
@@ -2066,11 +2066,11 @@
       <c r="G60" s="3">
         <v>117900</v>
       </c>
-      <c r="H60" s="3">
-        <v>147300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>143100</v>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J60" s="3">
         <v>3300</v>
@@ -2084,10 +2084,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>8700</v>
@@ -2096,10 +2096,10 @@
         <v>8700</v>
       </c>
       <c r="H61" s="3">
-        <v>11100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>1300</v>
@@ -2112,11 +2112,11 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>70000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>72900</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
         <v>73300</v>
@@ -2124,11 +2124,11 @@
       <c r="G62" s="3">
         <v>73800</v>
       </c>
-      <c r="H62" s="3">
-        <v>68100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>66200</v>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J62" s="3">
         <v>1900</v>
@@ -2228,11 +2228,11 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>226600</v>
-      </c>
-      <c r="E66" s="3">
-        <v>235800</v>
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F66" s="3">
         <v>231700</v>
@@ -2240,11 +2240,11 @@
       <c r="G66" s="3">
         <v>233200</v>
       </c>
-      <c r="H66" s="3">
-        <v>262000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>254600</v>
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J66" s="3">
         <v>6600</v>
@@ -2386,11 +2386,11 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-9400</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F72" s="3">
         <v>-41000</v>
@@ -2398,11 +2398,11 @@
       <c r="G72" s="3">
         <v>-41300</v>
       </c>
-      <c r="H72" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-5700</v>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J72" s="3">
         <v>-1200</v>
@@ -2502,11 +2502,11 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>190000</v>
-      </c>
-      <c r="E76" s="3">
-        <v>197700</v>
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F76" s="3">
         <v>176800</v>
@@ -2514,11 +2514,11 @@
       <c r="G76" s="3">
         <v>178000</v>
       </c>
-      <c r="H76" s="3">
-        <v>213400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>207400</v>
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J76" s="3">
         <v>29900</v>
@@ -2594,11 +2594,11 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>15900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>16500</v>
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F81" s="3">
         <v>-17600</v>
@@ -2606,11 +2606,11 @@
       <c r="G81" s="3">
         <v>-17800</v>
       </c>
-      <c r="H81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2300</v>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J81" s="3">
         <v>-800</v>
@@ -2810,11 +2810,11 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>6800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>7000</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>8</v>
@@ -2939,11 +2939,11 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-12800</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
@@ -3097,11 +3097,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>2400</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>8</v>
@@ -3156,10 +3156,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-3300</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
